--- a/tame_output/ON/bt/strategyON_20231031.xlsx
+++ b/tame_output/ON/bt/strategyON_20231031.xlsx
@@ -610,11 +610,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>81.9%</t>
+          <t>82.1%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>17.8%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.9%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>102.1%</t>
+          <t>102.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>97.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>22.6%</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>7.2%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>132.1%</t>
+          <t>132.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-10-29</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>126.1%</t>
+          <t>126.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>22.1%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1766"/>
+  <dimension ref="A1:G1767"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42128,7 +42128,7 @@
         <v>45228</v>
       </c>
       <c r="B1766" t="n">
-        <v>3.055022451738304</v>
+        <v>3.055423383477762</v>
       </c>
       <c r="C1766" t="n">
         <v>3.028879780391293</v>
@@ -42144,6 +42144,29 @@
       </c>
       <c r="G1766" t="n">
         <v>4.326833133323391</v>
+      </c>
+    </row>
+    <row r="1767">
+      <c r="A1767" s="2" t="n">
+        <v>45229</v>
+      </c>
+      <c r="B1767" t="n">
+        <v>3.056705830556029</v>
+      </c>
+      <c r="C1767" t="n">
+        <v>3.033268356072139</v>
+      </c>
+      <c r="D1767" t="n">
+        <v>1.542930473379503</v>
+      </c>
+      <c r="E1767" t="n">
+        <v>3.650084121110194</v>
+      </c>
+      <c r="F1767" t="n">
+        <v>2.164437302312861</v>
+      </c>
+      <c r="G1767" t="n">
+        <v>4.331930737459857</v>
       </c>
     </row>
   </sheetData>
